--- a/.alita/tests/loader_tests/files/Document_Index.xlsx
+++ b/.alita/tests/loader_tests/files/Document_Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epam-my.sharepoint.com/personal/swetha_bommalata_epam_com/Documents/EPAM/Grow/Java/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Aliaksei_Breilian/PycharmProjects/alita-sdk/.alita/tests/loader_tests/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D80D5A74-6A66-4F4E-9D42-C971EFDAB775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BA5D1D-6B5F-4D40-8AE4-FC2BF18E5C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-23400" windowWidth="38400" windowHeight="23400" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="106">
   <si>
     <t>Categories</t>
   </si>
@@ -126,12 +126,6 @@
     <t>Priority</t>
   </si>
   <si>
-    <t>Attachment</t>
-  </si>
-  <si>
-    <t> </t>
-  </si>
-  <si>
     <t>BG1</t>
   </si>
   <si>
@@ -152,9 +146,6 @@
     <t>High</t>
   </si>
   <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/21.png</t>
-  </si>
-  <si>
     <t>BG2</t>
   </si>
   <si>
@@ -173,9 +164,6 @@
   </si>
   <si>
     <t>Medium</t>
-  </si>
-  <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/6.png</t>
   </si>
   <si>
     <t>BG3</t>
@@ -200,9 +188,6 @@
     <t>Low</t>
   </si>
   <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/7.png</t>
-  </si>
-  <si>
     <t>BG4</t>
   </si>
   <si>
@@ -220,9 +205,6 @@
   </si>
   <si>
     <t>The text under the New User section is in English</t>
-  </si>
-  <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/11.png</t>
   </si>
   <si>
     <t>BG5</t>
@@ -245,9 +227,6 @@
     <t>The comment is posted under the product</t>
   </si>
   <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/23.png</t>
-  </si>
-  <si>
     <t>BG6</t>
   </si>
   <si>
@@ -264,9 +243,6 @@
   </si>
   <si>
     <t>The manufacturer link shows an appropriate page</t>
-  </si>
-  <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/11/Fn3.png</t>
   </si>
   <si>
     <t>BG7</t>
@@ -289,9 +265,6 @@
     <t>The product quantity can be increased past 2</t>
   </si>
   <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/1.png</t>
-  </si>
-  <si>
     <t>BG8</t>
   </si>
   <si>
@@ -312,9 +285,6 @@
     <t>A list of products in the selected price range is shown</t>
   </si>
   <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/F4.png</t>
-  </si>
-  <si>
     <t>BG9</t>
   </si>
   <si>
@@ -337,9 +307,6 @@
     <t>The caption of the "Return to Store" button is written with even spacing between letters</t>
   </si>
   <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/15.png</t>
-  </si>
-  <si>
     <t>BG11</t>
   </si>
   <si>
@@ -358,9 +325,6 @@
     <t>The currency is changed as expected</t>
   </si>
   <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/22.png</t>
-  </si>
-  <si>
     <t>BG12</t>
   </si>
   <si>
@@ -385,9 +349,6 @@
     <t>The Sign In button is above the footer</t>
   </si>
   <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/F9.png</t>
-  </si>
-  <si>
     <t>BG14</t>
   </si>
   <si>
@@ -406,9 +367,6 @@
   </si>
   <si>
     <t>The short description and description of the product are in English</t>
-  </si>
-  <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/Find-13.png</t>
   </si>
   <si>
     <t>BG16</t>
@@ -429,9 +387,6 @@
     <t>The twitter share button shows an appropriate page</t>
   </si>
   <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/5.png</t>
-  </si>
-  <si>
     <t>BG17</t>
   </si>
   <si>
@@ -450,9 +405,6 @@
     <t>The user is able to share the product through My Space</t>
   </si>
   <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/20.png</t>
-  </si>
-  <si>
     <t>BG18</t>
   </si>
   <si>
@@ -469,16 +421,13 @@
   </si>
   <si>
     <t>The yellow and orange colors are spelled correctly</t>
-  </si>
-  <si>
-    <t>https://academybugs.com/wp-content/uploads/2020/10/14.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -506,12 +455,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -698,7 +641,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -713,47 +656,40 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1038,15 +974,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="71" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="1"/>
+    <col min="4" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1057,7 +993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="57.6">
+    <row r="2" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1068,7 +1004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="91.5">
+    <row r="3" spans="1:3" ht="96" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1079,7 +1015,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45.75">
+    <row r="4" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1090,7 +1026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1101,7 +1037,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="45.75">
+    <row r="6" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1112,7 +1048,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="57.6">
+    <row r="7" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -1133,899 +1069,471 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC5B8A8C-0441-4F44-8C37-926B33983C91}">
-  <dimension ref="A1:Y20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="47.85546875" customWidth="1"/>
-    <col min="5" max="5" width="33.5703125" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
+    <col min="1" max="4" width="47.83203125" customWidth="1"/>
+    <col min="5" max="5" width="33.5" customWidth="1"/>
+    <col min="6" max="6" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18.75">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="61" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="B2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="T1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="U1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="V1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="W1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="X1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y1" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="56.25">
-      <c r="A2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="E2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="F2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="G2" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="46" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="14">
+      <c r="C3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="106" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="76" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="91" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="15">
         <v>1</v>
       </c>
-      <c r="H2" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="17"/>
-    </row>
-    <row r="3" spans="1:25" ht="42">
-      <c r="A3" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="15" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="61" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="14">
+      <c r="G7" s="14">
         <v>2</v>
       </c>
-      <c r="H3" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17"/>
-      <c r="V3" s="17"/>
-      <c r="W3" s="17"/>
-      <c r="X3" s="17"/>
-      <c r="Y3" s="17"/>
-    </row>
-    <row r="4" spans="1:25" ht="98.25">
-      <c r="A4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="14" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="91" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="106" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="91" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="76" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="14">
+      <c r="G11" s="14">
         <v>3</v>
       </c>
-      <c r="H4" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="17"/>
-    </row>
-    <row r="5" spans="1:25" ht="70.5">
-      <c r="A5" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="14" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="61" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="61" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="91" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C15" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D15" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E15" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="18">
+      <c r="F15" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="46" x14ac:dyDescent="0.2">
+      <c r="A16" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="61" x14ac:dyDescent="0.2">
+      <c r="A17" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="61" x14ac:dyDescent="0.2">
+      <c r="A18" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="23">
         <v>3</v>
       </c>
-      <c r="H5" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-    </row>
-    <row r="6" spans="1:25" ht="84.75">
-      <c r="A6" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="20">
-        <v>1</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-    </row>
-    <row r="7" spans="1:25" ht="56.25">
-      <c r="A7" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="18">
-        <v>2</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-      <c r="T7" s="17"/>
-      <c r="U7" s="17"/>
-      <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
-      <c r="X7" s="17"/>
-      <c r="Y7" s="17"/>
-    </row>
-    <row r="8" spans="1:25" ht="84.75">
-      <c r="A8" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="20">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-    </row>
-    <row r="9" spans="1:25" ht="126.75">
-      <c r="A9" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="18">
-        <v>2</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-    </row>
-    <row r="10" spans="1:25" ht="84.75">
-      <c r="A10" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="20">
-        <v>1</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-    </row>
-    <row r="11" spans="1:25" ht="70.5">
-      <c r="A11" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="18">
+    </row>
+    <row r="19" spans="1:7" ht="61" x14ac:dyDescent="0.2">
+      <c r="A19" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="23">
         <v>3</v>
       </c>
-      <c r="H11" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-    </row>
-    <row r="12" spans="1:25" ht="56.25">
-      <c r="A12" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="20">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-    </row>
-    <row r="13" spans="1:25" ht="56.25">
-      <c r="A13" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="21">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-    </row>
-    <row r="14" spans="1:25" ht="15" customHeight="1">
-      <c r="A14" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="25">
-        <v>3</v>
-      </c>
-      <c r="H14" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="17"/>
-      <c r="Y14" s="17"/>
-    </row>
-    <row r="15" spans="1:25" ht="84.75">
-      <c r="A15" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="29">
-        <v>1</v>
-      </c>
-      <c r="H15" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="17"/>
-    </row>
-    <row r="16" spans="1:25" ht="42">
-      <c r="A16" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="29">
-        <v>2</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="17"/>
-      <c r="U16" s="17"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
-      <c r="X16" s="17"/>
-      <c r="Y16" s="17"/>
-    </row>
-    <row r="17" spans="1:25" ht="56.25">
-      <c r="A17" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="29">
-        <v>2</v>
-      </c>
-      <c r="H17" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
-      <c r="X17" s="17"/>
-      <c r="Y17" s="17"/>
-    </row>
-    <row r="18" spans="1:25" ht="56.25">
-      <c r="A18" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="29">
-        <v>3</v>
-      </c>
-      <c r="H18" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="17"/>
-      <c r="U18" s="17"/>
-      <c r="V18" s="17"/>
-      <c r="W18" s="17"/>
-      <c r="X18" s="17"/>
-      <c r="Y18" s="17"/>
-    </row>
-    <row r="19" spans="1:25" ht="56.25">
-      <c r="A19" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="29">
-        <v>3</v>
-      </c>
-      <c r="H19" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-    </row>
-    <row r="20" spans="1:25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{A522583F-DA6C-449B-B676-13A516C541DA}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{E595EF9E-3A24-4F30-B930-CB2D7E423F76}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{B27AAB96-4DB9-4F04-8E68-DA1DD6E2447B}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{ADDDC3B5-52AC-4717-A8C6-E2C47F09B1B9}"/>
-    <hyperlink ref="H6" r:id="rId5" xr:uid="{42C60ECD-3E88-47F6-A340-B6DBB1D95913}"/>
-    <hyperlink ref="H7" r:id="rId6" xr:uid="{CF6DC238-4083-4FAB-8928-092B1D8DAF6E}"/>
-    <hyperlink ref="H8" r:id="rId7" xr:uid="{20EBD0C1-B390-4F2E-90A7-A2D9376D1A5D}"/>
-    <hyperlink ref="H9" r:id="rId8" xr:uid="{506D3190-43C7-4979-ACF9-AAE5CE9755C7}"/>
-    <hyperlink ref="H10" r:id="rId9" xr:uid="{753D9DFC-6016-4C34-ACCF-30F34B2C161F}"/>
-    <hyperlink ref="H11" r:id="rId10" xr:uid="{0D52D590-60FD-4528-8A4F-CA59AC844CFB}"/>
-    <hyperlink ref="H12" r:id="rId11" xr:uid="{D032B297-51A7-400B-89C1-6FF6D3E99C8E}"/>
-    <hyperlink ref="H13" r:id="rId12" xr:uid="{0EE4F5EA-1910-4310-8732-08A9D3AAA842}"/>
-    <hyperlink ref="H14" r:id="rId13" xr:uid="{4A105CB1-7FA1-4F70-A293-4E91A3F90B7D}"/>
-    <hyperlink ref="H15" r:id="rId14" xr:uid="{A2A31B42-7B25-4F9B-850D-B6D36D210050}"/>
-    <hyperlink ref="H16" r:id="rId15" xr:uid="{06FC8968-50DD-427C-807B-2260A037DE79}"/>
-    <hyperlink ref="H17" r:id="rId16" xr:uid="{E8F7CF90-60AE-454C-9E88-83FC3DF7641C}"/>
-    <hyperlink ref="H18" r:id="rId17" xr:uid="{A2075C2F-3907-4CBD-A55C-42906C5E0347}"/>
-    <hyperlink ref="H19" r:id="rId18" xr:uid="{BE20AEB5-DB19-48D9-8036-9AD8E3372B3E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010071802037AD89BC4C9ABF9D4D12B27F21" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5a36bbcbd3a008c84bc4c6e634e764f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a236750a-f2cd-4964-8b71-208751f266d3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0fb357aff33d4dc841e6b00f62f31955" ns2:_="">
     <xsd:import namespace="a236750a-f2cd-4964-8b71-208751f266d3"/>
@@ -2163,12 +1671,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2179,13 +1681,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59CAFABE-B090-44B0-B02E-82DC253A2F3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC1682B-D1C5-4FCE-BDCB-C851D4C8C5DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC1682B-D1C5-4FCE-BDCB-C851D4C8C5DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59CAFABE-B090-44B0-B02E-82DC253A2F3C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a236750a-f2cd-4964-8b71-208751f266d3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C25D3F11-937F-4E92-9768-A6C246A636FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C25D3F11-937F-4E92-9768-A6C246A636FF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>